--- a/artfynd/A 62760-2025 artfynd.xlsx
+++ b/artfynd/A 62760-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106451713</v>
+        <v>106450414</v>
       </c>
       <c r="B2" t="n">
-        <v>101752</v>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flenvike, Storhagen NO, Gtl</t>
+          <t>Kappelshamn knappt 1,9 km NNV, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723512</v>
+        <v>723803</v>
       </c>
       <c r="R2" t="n">
-        <v>6420244</v>
+        <v>6420248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>. Nattplats vid tippen nattplatsen vid tippen [enl karta 27:480,85, har även noterat vid 794 men trol missförstånd]</t>
+          <t>.  Vid orientering till 793, 27:480,114</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,45 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106450414</v>
+        <v>106451713</v>
       </c>
       <c r="B3" t="n">
-        <v>98681</v>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kappelshamn knappt 1,9 km NNV, Gtl</t>
+          <t>Flenvike, Storhagen NO, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723803</v>
+        <v>723512</v>
       </c>
       <c r="R3" t="n">
-        <v>6420248</v>
+        <v>6420244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>.  Vid orientering till 793, 27:480,114</t>
+          <t>. Nattplats vid tippen nattplatsen vid tippen [enl karta 27:480,85, har även noterat vid 794 men trol missförstånd]</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 62760-2025 artfynd.xlsx
+++ b/artfynd/A 62760-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106450414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106451713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>